--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487629_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487629_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5356</v>
+        <v>8.3973</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7683</v>
+        <v>6.7663</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7673</v>
+        <v>1.631</v>
       </c>
       <c r="G2" t="n">
         <v>4.3234</v>
@@ -610,13 +610,13 @@
         <v>3.2985</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9614</v>
+        <v>1.8231</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9445</v>
+        <v>1.9425</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0168</v>
+        <v>-0.1194</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6597</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.576</v>
+        <v>1.9298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7242</v>
+        <v>0.0235</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8517</v>
+        <v>1.9062</v>
       </c>
       <c r="G3" t="n">
         <v>-1.487</v>
@@ -688,13 +688,13 @@
         <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>2.257</v>
+        <v>1.6108</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8521</v>
+        <v>2.1514</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5951</v>
+        <v>-0.5406</v>
       </c>
       <c r="V3" t="n">
         <v>1.2239</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9726</v>
+        <v>1.785</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1256</v>
+        <v>0.6496</v>
       </c>
       <c r="F4" t="n">
-        <v>0.847</v>
+        <v>1.1354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7359</v>
+        <v>1.9944</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1031</v>
+        <v>1.188</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8391</v>
+        <v>0.8064</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9553</v>
+        <v>2.152</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3666</v>
+        <v>0.2389</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3219</v>
+        <v>1.9131</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2194</v>
+        <v>-0.1576</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7366</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5172</v>
+        <v>-1.1067</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2985</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2546</v>
+        <v>-0.7153</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6808</v>
+        <v>-0.0979</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4262</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5642</v>
+        <v>0.894</v>
       </c>
       <c r="W4" t="n">
-        <v>1.788</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. VILLAMANDOS TORRES</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6722</v>
+        <v>1.4062</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4817</v>
+        <v>1.4848</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1539</v>
+        <v>-0.0786</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7237</v>
+        <v>1.3744</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.7509</v>
+        <v>-0.3773</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0271</v>
+        <v>1.7518</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.8115</v>
+        <v>1.4202</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.5828</v>
+        <v>0.0577</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7713</v>
+        <v>1.3625</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0877</v>
+        <v>-0.0458</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1681</v>
+        <v>-0.435</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2558</v>
+        <v>0.3893</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8497</v>
+        <v>0.1974</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3358</v>
+        <v>0.3348</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5139</v>
+        <v>-0.1374</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1283</v>
+        <v>-0.9418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1283</v>
+        <v>0.894</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2689</v>
+        <v>1.373</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4838</v>
+        <v>0.526</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2149</v>
+        <v>0.847</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3744</v>
+        <v>0.7359</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3773</v>
+        <v>-1.1031</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7518</v>
+        <v>1.8391</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4202</v>
+        <v>0.9553</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0577</v>
+        <v>-0.3666</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3625</v>
+        <v>1.3219</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0458</v>
+        <v>-0.2194</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.435</v>
+        <v>-0.7366</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3893</v>
+        <v>0.5172</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1642</v>
+        <v>-3.2985</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9403</v>
+        <v>2.7164</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9399</v>
+        <v>0.655</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6662</v>
+        <v>1.0812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2736</v>
+        <v>-0.4262</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9418</v>
+        <v>0.5642</v>
       </c>
       <c r="W6" t="n">
-        <v>0.894</v>
+        <v>1.788</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8358</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>M. VILLAMANDOS TORRES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2146</v>
+        <v>0.0265</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5121</v>
+        <v>-1.8821</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7266</v>
+        <v>1.9086</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9944</v>
+        <v>-1.7237</v>
       </c>
       <c r="H7" t="n">
-        <v>1.188</v>
+        <v>-2.7509</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8064</v>
+        <v>1.0271</v>
       </c>
       <c r="J7" t="n">
-        <v>2.152</v>
+        <v>-1.8115</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2389</v>
+        <v>-2.5828</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9131</v>
+        <v>0.7713</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1576</v>
+        <v>0.0877</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9491000000000001</v>
+        <v>-0.1681</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1067</v>
+        <v>0.2558</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>-2.1344</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5224</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2858</v>
+        <v>1.204</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2596</v>
+        <v>0.9354</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0262</v>
+        <v>0.2686</v>
       </c>
       <c r="V7" t="n">
-        <v>0.894</v>
+        <v>1.1283</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>1.1283</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2735</v>
+        <v>-0.1762</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0425</v>
+        <v>0.3032</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3159</v>
+        <v>-0.4794</v>
       </c>
       <c r="G8" t="n">
         <v>0.4689</v>
@@ -1078,13 +1078,13 @@
         <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9827</v>
+        <v>-0.8855</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1806</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8021</v>
+        <v>-0.9656</v>
       </c>
       <c r="V8" t="n">
         <v>-1.506</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5795</v>
+        <v>-0.6538</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3209</v>
+        <v>0.9341</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9003</v>
+        <v>-1.5878</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2912</v>
+        <v>1.5732</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9402</v>
+        <v>1.2712</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.649</v>
+        <v>0.302</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4206</v>
+        <v>2.3089</v>
       </c>
       <c r="K9" t="n">
-        <v>1.38</v>
+        <v>1.0504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0406</v>
+        <v>1.2585</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1294</v>
+        <v>-0.7358</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5602</v>
+        <v>0.2208</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6896</v>
+        <v>-0.9565</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1229</v>
+        <v>-1.2374</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4116</v>
+        <v>-0.445</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2887</v>
+        <v>-0.7924</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5537</v>
+        <v>-0.9896</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2821</v>
+        <v>0.2343</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8358</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0597</v>
+        <v>-1.0701</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7734</v>
+        <v>0.3209</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8331</v>
+        <v>-1.3909</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5732</v>
+        <v>1.2912</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2712</v>
+        <v>1.9402</v>
       </c>
       <c r="I10" t="n">
-        <v>0.302</v>
+        <v>-0.649</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3089</v>
+        <v>1.4206</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0504</v>
+        <v>1.38</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2585</v>
+        <v>0.0406</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7358</v>
+        <v>-0.1294</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2208</v>
+        <v>0.5602</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9565</v>
+        <v>-0.6896</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6433</v>
+        <v>-0.6135</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>-0.4116</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0377</v>
+        <v>-0.2019</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9896</v>
+        <v>-1.5537</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2343</v>
+        <v>0.2821</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2239</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8734</v>
+        <v>-1.5671</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5627</v>
+        <v>-1.2019</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3107</v>
+        <v>-0.3652</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7244</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4491</v>
+        <v>-0.1427</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3511</v>
+        <v>0.0098</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.098</v>
+        <v>-0.1525</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2821</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5049</v>
+        <v>-4.199</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8658</v>
+        <v>-3.8052</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6391</v>
+        <v>-0.3938</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0377</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8374</v>
+        <v>-1.5315</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8356</v>
+        <v>-0.775</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0018</v>
+        <v>-0.7565</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6597</v>
@@ -1423,43 +1423,43 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.948900000000001</v>
+        <v>7.2516</v>
       </c>
       <c r="E13" t="n">
-        <v>3.816400000000002</v>
+        <v>4.1192</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1325</v>
+        <v>3.132499999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>5.788599999999999</v>
+        <v>5.788600000000001</v>
       </c>
       <c r="H13" t="n">
         <v>1.8126</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9763</v>
+        <v>3.976300000000001</v>
       </c>
       <c r="J13" t="n">
         <v>9.5047</v>
       </c>
       <c r="K13" t="n">
-        <v>1.301799999999999</v>
+        <v>1.3018</v>
       </c>
       <c r="L13" t="n">
-        <v>8.2028</v>
+        <v>8.202799999999998</v>
       </c>
       <c r="M13" t="n">
         <v>-3.7163</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5105000000000001</v>
+        <v>0.5105</v>
       </c>
       <c r="O13" t="n">
         <v>-4.226599999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>3.8806</v>
+        <v>3.880599999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.4928</v>
@@ -1468,10 +1468,10 @@
         <v>20.3733</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06159999999999966</v>
+        <v>0.3643999999999996</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5028</v>
+        <v>4.8058</v>
       </c>
       <c r="U13" t="n">
         <v>-4.4413</v>
@@ -1483,7 +1483,7 @@
         <v>6.3014</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.083499999999999</v>
+        <v>-9.083500000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5255</v>
+        <v>3.08</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7054</v>
+        <v>2.5052</v>
       </c>
       <c r="F14" t="n">
-        <v>0.82</v>
+        <v>0.5747</v>
       </c>
       <c r="G14" t="n">
         <v>2.3351</v>
@@ -1546,13 +1546,13 @@
         <v>0.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2963</v>
+        <v>-0.1492</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1222</v>
+        <v>-0.078</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1741</v>
+        <v>-0.0712</v>
       </c>
       <c r="V14" t="n">
         <v>0.894</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>T. PUNZANO VIEDMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9837</v>
+        <v>1.1151</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1546</v>
+        <v>2.2084</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1383</v>
+        <v>-1.0933</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1184</v>
+        <v>0.1345</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.6233</v>
+        <v>-1.2391</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5049</v>
+        <v>1.3737</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.7882</v>
+        <v>1.2938</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.0318</v>
+        <v>-1.1699</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2436</v>
+        <v>2.4637</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3302</v>
+        <v>-1.1592</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5916</v>
+        <v>-0.0692</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2614</v>
+        <v>-1.09</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3881</v>
+        <v>1.9403</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1126</v>
+        <v>0.2641</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3501</v>
+        <v>0.6325</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7625</v>
+        <v>-0.3684</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6015</v>
+        <v>-1.2239</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3776</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1437</v>
+        <v>0.9517</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3055</v>
+        <v>-2.1566</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1618</v>
+        <v>3.1082</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2253</v>
+        <v>-3.1184</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0274</v>
+        <v>-3.6233</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1979</v>
+        <v>0.5049</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6342</v>
+        <v>-2.7882</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5808</v>
+        <v>-3.0318</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0533</v>
+        <v>0.2436</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.3302</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4466</v>
+        <v>-0.5916</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1446</v>
+        <v>0.2614</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1344</v>
+        <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5027</v>
+        <v>2.0805</v>
       </c>
       <c r="T16" t="n">
-        <v>0.074</v>
+        <v>1.3481</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5767</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7075</v>
+        <v>1.6015</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8358</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1283</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. PUNZANO VIEDMA</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0446</v>
+        <v>0.7894</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4076</v>
+        <v>0.7059</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.363</v>
+        <v>0.0835</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1345</v>
+        <v>-1.2253</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2391</v>
+        <v>-1.0274</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3737</v>
+        <v>-0.1979</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2938</v>
+        <v>-0.6342</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1699</v>
+        <v>-0.5808</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4637</v>
+        <v>-0.0533</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1592</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0692</v>
+        <v>-0.4466</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.09</v>
+        <v>-0.1446</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8064</v>
+        <v>0.143</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1683</v>
+        <v>0.4744</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6381</v>
+        <v>-0.3314</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2239</v>
+        <v>0.7075</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2821</v>
+        <v>1.8358</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.506</v>
+        <v>-1.1283</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1483</v>
+        <v>0.3795</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.199</v>
+        <v>0.3015</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0507</v>
+        <v>0.078</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7593</v>
@@ -1858,13 +1858,13 @@
         <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6009</v>
+        <v>-0.0732</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3768</v>
+        <v>0.8773</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9778</v>
+        <v>-0.9505</v>
       </c>
       <c r="V18" t="n">
         <v>0.0478</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0959</v>
+        <v>-1.1222</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8843</v>
+        <v>-0.49</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9802</v>
+        <v>-0.6322</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1924</v>
+        <v>-1.9217</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4894</v>
+        <v>-1.3767</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6817</v>
+        <v>-0.545</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1553</v>
+        <v>-1.2811</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0742</v>
+        <v>-1.2811</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3477</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4152</v>
+        <v>-0.0956</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7629</v>
+        <v>-0.545</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0785</v>
+        <v>-0.5885</v>
       </c>
       <c r="T19" t="n">
-        <v>0.729</v>
+        <v>0.1792</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6505</v>
+        <v>-0.7677</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5642</v>
+        <v>0.6119</v>
       </c>
       <c r="W19" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.5642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>G. FATA ALCARAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3407</v>
+        <v>-1.1247</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7903</v>
+        <v>-0.0842</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5504</v>
+        <v>-1.0404</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9217</v>
+        <v>0.6458</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3767</v>
+        <v>1.8059</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.545</v>
+        <v>-1.1601</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2811</v>
+        <v>0.7637</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2811</v>
+        <v>0.7003</v>
       </c>
       <c r="L20" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.1179</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.1056</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-1.2235</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.7705</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.8927</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.6119</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
-        <v>-0.6405999999999999</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-0.0956</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-0.545</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.7761</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.7761</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-0.8071</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.1211</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.6859</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.6119</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.6119</v>
-      </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. FATA ALCARAZ</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4217</v>
+        <v>-1.4518</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0842</v>
+        <v>-1.6222</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3374</v>
+        <v>0.1705</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6458</v>
+        <v>-1.247</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8059</v>
+        <v>-2.1173</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1601</v>
+        <v>0.8703</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7637</v>
+        <v>-0.2762</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7003</v>
+        <v>-1.6971</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0634</v>
+        <v>1.4209</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1179</v>
+        <v>-0.9708</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1056</v>
+        <v>-0.4202</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2235</v>
+        <v>-0.5506</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>-3.6866</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-4.8508</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0675</v>
+        <v>0.4699</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1222</v>
+        <v>0.4929</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1897</v>
+        <v>-0.023</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6119</v>
+        <v>3.0119</v>
       </c>
       <c r="W21" t="n">
+        <v>3.0119</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.6119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0104</v>
+        <v>-1.7327</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4389</v>
+        <v>0.3838</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5715</v>
+        <v>-2.1165</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3813</v>
+        <v>-1.1924</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1409</v>
+        <v>0.4894</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5222</v>
+        <v>-1.6817</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7437</v>
+        <v>0.1553</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7209</v>
+        <v>0.0742</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0228</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.125</v>
+        <v>-1.3477</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.58</v>
+        <v>0.4152</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.545</v>
+        <v>-1.7629</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1828</v>
+        <v>-0.5583</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2423</v>
+        <v>0.2285</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0595</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1537</v>
+        <v>-2.0827</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.946</v>
+        <v>-1.2387</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2077</v>
+        <v>-0.8441</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3365</v>
+        <v>-0.3813</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9954</v>
+        <v>0.1409</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6589</v>
+        <v>-0.5222</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0731</v>
+        <v>0.7437</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9691</v>
+        <v>0.7209</v>
       </c>
       <c r="L23" t="n">
-        <v>0.104</v>
+        <v>0.0228</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7366</v>
+        <v>-1.125</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0263</v>
+        <v>-0.58</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7629</v>
+        <v>-0.545</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9105</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.8508</v>
+        <v>-1.9403</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6068</v>
+        <v>-0.2551</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6079</v>
+        <v>-0.0421</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0011</v>
+        <v>-0.2131</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1865</v>
+        <v>-0.2821</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4104</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2676</v>
+        <v>-2.5289</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2228</v>
+        <v>-2.2993</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0448</v>
+        <v>-0.2296</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.247</v>
+        <v>0.6047</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1173</v>
+        <v>0.2521</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8703</v>
+        <v>0.3526</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2762</v>
+        <v>0.6126</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6971</v>
+        <v>0.1153</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4209</v>
+        <v>0.4972</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9708</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4202</v>
+        <v>0.1367</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5506</v>
+        <v>-0.1446</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.6866</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.8508</v>
+        <v>-2.9105</v>
       </c>
       <c r="R24" t="n">
         <v>1.1642</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3459</v>
+        <v>-0.1635</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1077</v>
+        <v>-0.0014</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2382</v>
+        <v>-0.162</v>
       </c>
       <c r="V24" t="n">
-        <v>3.0119</v>
+        <v>-1.2239</v>
       </c>
       <c r="W24" t="n">
-        <v>3.0119</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.208</v>
+        <v>-2.5541</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5996</v>
+        <v>-1.3464</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6083</v>
+        <v>-1.2077</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6047</v>
+        <v>0.3365</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2521</v>
+        <v>1.9954</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3526</v>
+        <v>-1.6589</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6126</v>
+        <v>2.0731</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1153</v>
+        <v>1.9691</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4972</v>
+        <v>0.104</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-1.7366</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1367</v>
+        <v>0.0263</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1446</v>
+        <v>-1.7629</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.7463</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9105</v>
+        <v>-4.8508</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8425</v>
+        <v>0.2064</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3017</v>
+        <v>0.2075</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.0011</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2239</v>
+        <v>-0.1865</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2239</v>
+        <v>-1.4104</v>
       </c>
     </row>
     <row r="26">
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.948800000000001</v>
+        <v>-6.281400000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1326</v>
+        <v>-3.132600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.8161</v>
+        <v>-3.1489</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.788799999999998</v>
+        <v>-5.7888</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.8124</v>
+        <v>-1.812400000000001</v>
       </c>
       <c r="I26" t="n">
         <v>-3.9762</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7162</v>
+        <v>3.716200000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5105000000000002</v>
+        <v>-0.5105</v>
       </c>
       <c r="L26" t="n">
         <v>4.2268</v>
@@ -2473,7 +2473,7 @@
         <v>-8.2029</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.880700000000001</v>
+        <v>-3.8807</v>
       </c>
       <c r="Q26" t="n">
         <v>-20.3735</v>
@@ -2482,22 +2482,22 @@
         <v>16.4928</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0616000000000011</v>
+        <v>0.6055999999999997</v>
       </c>
       <c r="T26" t="n">
-        <v>4.441099999999999</v>
+        <v>4.4411</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.5027</v>
+        <v>-3.8355</v>
       </c>
       <c r="V26" t="n">
-        <v>2.782099999999999</v>
+        <v>2.782100000000001</v>
       </c>
       <c r="W26" t="n">
         <v>9.083500000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.301399999999999</v>
+        <v>-6.3014</v>
       </c>
     </row>
   </sheetData>
